--- a/sources/jin_step3.xlsx
+++ b/sources/jin_step3.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -459,12 +459,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">

--- a/sources/jin_step3.xlsx
+++ b/sources/jin_step3.xlsx
@@ -774,6 +774,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
@@ -806,6 +811,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
@@ -843,6 +853,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
@@ -880,6 +895,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
@@ -917,6 +937,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
@@ -954,6 +979,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>cda82971-a307-467e-ad05-57768181324c</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
@@ -996,6 +1026,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
@@ -1033,6 +1068,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
@@ -1068,6 +1108,11 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6556,6 +6601,11 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
@@ -6583,6 +6633,11 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
+        </is>
+      </c>
       <c r="O130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
@@ -6610,6 +6665,11 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
@@ -6637,6 +6697,11 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
@@ -6664,6 +6729,11 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
@@ -6691,6 +6761,11 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
@@ -6718,6 +6793,11 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
@@ -6745,6 +6825,11 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
@@ -6772,6 +6857,11 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
@@ -6797,6 +6887,11 @@
       <c r="I138" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
